--- a/data/sample/示例数据/附件5：研报数据/字段说明.xlsx
+++ b/data/sample/示例数据/附件5：研报数据/字段说明.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="个股_研报信息" sheetId="1" r:id="rId1"/>
